--- a/extenbooks/S1501_extenbook.xlsx
+++ b/extenbooks/S1501_extenbook.xlsx
@@ -9322,7 +9322,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -10450,11 +10450,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10477,64 +10477,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Chapter 15 series S1501</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>extenbook_published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S1501_research.json", "adequacy_report": "Technical/docs/chapters/CH15_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S1501_DPR.md", "epr": "Technical/docs/series/S1501_EPR.md", "loader": "Technical/code/L01_loaders/L01_S1501_load.py", "processor": "Technical/code/P02_processors/P02_S1501_construct.py", "validator": "Technical/code/V03_validators/V03_S1501_validate.py", "processed": "Technical/data/processed/S1501.parquet", "chopped_csv": "Technical/chopped/S1501.csv", "extenbook_xlsx": "Technical/extenbooks/S1501_extenbook.xlsx"}</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S1501_extenbook.xlsx
+++ b/extenbooks/S1501_extenbook.xlsx
@@ -9269,7 +9269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A149"/>
+  <dimension ref="A1:A151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -9308,7 +9308,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>**Phase**: 5 (Ingestion)</t>
+          <t>**Pipeline stage**: Ingestion</t>
         </is>
       </c>
     </row>
@@ -9336,7 +9336,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>**Author**: opus-subagent-fanout-ch15</t>
+          <t>**Author**: RSCD replication pipeline (automated)</t>
         </is>
       </c>
     </row>
@@ -9458,38 +9458,38 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>| Subseries | Coverage | Publisher / Series ID | Native units | Retrieval |</t>
+          <t>*Each series is built from sub-components identified by a suffix on the series ID (for example, S1501-A, S1501-B); they are listed below.*</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>|---|---|---|---|---|</t>
-        </is>
-      </c>
+      <c r="A34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>| **S1501-A** | 1774-2011 | MeasuringWorth (Officer &amp; Williamson), USCPI annual series | Index 1982-84 = 100 | Salvaged chopped table `Appendix15_MeasuringWorthCPI.xlsx` (column `U.S. Consumer Price Index`) |</t>
+          <t>| Subseries | Coverage | Publisher / Series ID | Native units | Retrieval |</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>| **S1501-B** | 2012-2025 | FRED `CPIAUCNS` (BLS CPI-U All Urban Consumers, NSA) | Index 1982-84 = 100 | Live API: `https://api.stlouisfed.org/fred/series/observations?series_id=CPIAUCNS`; annual frequency = arithmetic mean of monthly values |</t>
+          <t>|---|---|---|---|---|</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>| **S1501-A** | 1774-2011 | MeasuringWorth (Officer &amp; Williamson), USCPI annual series | Index 1982-84 = 100 | Salvaged chopped table `Appendix15_MeasuringWorthCPI.xlsx` (column `U.S. Consumer Price Index`) |</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>## 4. Construction</t>
+          <t>| **S1501-B** | 2012-2025 | FRED `CPIAUCNS` (BLS CPI-U All Urban Consumers, NSA) | Index 1982-84 = 100 | Live API: `https://api.stlouisfed.org/fred/series/observations?series_id=CPIAUCNS`; annual frequency = arithmetic mean of monthly values |</t>
         </is>
       </c>
     </row>
@@ -9499,7 +9499,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S1501 is **direct** (Anu sense): a single observed annual index with a single forward-extension subsource on the same index base.</t>
+          <t>## 4. Construction</t>
         </is>
       </c>
     </row>
@@ -9509,69 +9509,69 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>S1501 is **direct** (in this project's construction taxonomy): a single observed annual index with a single forward-extension subsource on the same index base.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>1. **Load** S1501-A (MeasuringWorth USCPI) for 1774-2011.</t>
         </is>
       </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>2. **Extend** (Phase 6) with S1501-B (FRED CPIAUCNS), reindexed to the MeasuringWorth value at the most recent overlap year (default 2011). Because both series share the BLS CPI-U as their post-1913 backbone on the same 1982-84 base, the scale factor is expected to be ~1.000.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>**Formula** (none — direct, with overlap-anchor splice for extension):</t>
+          <t>2. **Extend** (a later enrichment pass) with S1501-B (FRED CPIAUCNS), reindexed to the MeasuringWorth value at the most recent overlap year (default 2011). Because both series share the BLS CPI-U as their post-1913 backbone on the same 1982-84 base, the scale factor is expected to be ~1.000.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>```</t>
-        </is>
-      </c>
+      <c r="A46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S1501[year] =</t>
+          <t>**Formula** (none — direct, with overlap-anchor splice for extension):</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">  IF year in [1774, 2011] : MeasuringWorth_USCPI[year]</t>
+          <t>```</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">  IF year in [2012, 2025] : FRED_CPIAUCNS[year] * (S1501[overlap_year] / FRED_CPIAUCNS[overlap_year])</t>
+          <t>S1501[year] =</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>```</t>
+          <t xml:space="preserve">  IF year in [1774, 2011] : MeasuringWorth_USCPI[year]</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr"/>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  IF year in [2012, 2025] : FRED_CPIAUCNS[year] * (S1501[overlap_year] / FRED_CPIAUCNS[overlap_year])</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>## 5. Year coverage</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -9581,38 +9581,38 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>- **Book period**: 1774-2011 (annual) — 238 observations</t>
+          <t>## 5. Year coverage</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>- **Extension period**: 2012-2025 (annual) — 14 observations target</t>
-        </is>
-      </c>
+      <c r="A55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>- **Total coverage**: 1774-2025 — up to 252 observations</t>
+          <t>- **Book period**: 1774-2011 (annual) — 238 observations</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>- **Gaps**: none expected in the book period.</t>
+          <t>- **Extension period**: 2012-2025 (annual) — 14 observations target</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr"/>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>- **Total coverage**: 1774-2025 — up to 252 observations</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>## 6. Units</t>
+          <t>- **Gaps**: none expected in the book period.</t>
         </is>
       </c>
     </row>
@@ -9622,7 +9622,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>- **S1501 (final)**: Index, 1982-84 = 100 (BLS CPI-U convention).</t>
+          <t>## 6. Units</t>
         </is>
       </c>
     </row>
@@ -9632,7 +9632,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>## 7. Caveats</t>
+          <t>- **S1501 (final)**: Index, 1982-84 = 100 (BLS CPI-U convention).</t>
         </is>
       </c>
     </row>
@@ -9642,31 +9642,31 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1. **Pre-1913 reconstruction**: the 1774-1912 segment is Officer &amp; Williamson's editorial splice of multiple historical series (Warren-Pearson wholesale price index reweighted to consumer proxy, etc.). The 1913+ segment is direct BLS CPI-U. We do not re-do the editorial splice — we use MeasuringWorth's published series as Shaikh did.</t>
+          <t>## 7. Caveats</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>2. **License**: MeasuringWorth's permitted-academic-use license requires citing Officer &amp; Williamson and prohibits commercial redistribution. The post-1913 BLS CPI-U (FRED `CPIAUCNS`) is the open-license fallback for the modern segment; MeasuringWorth's pre-1913 segment is what makes the long-run series unique.</t>
-        </is>
-      </c>
+      <c r="A66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>3. **No proxy substitution**: Both subseries are CPI on the same base. The extension is the same BLS CPI-U that MeasuringWorth uses as its post-1913 backbone.</t>
+          <t>1. **Pre-1913 reconstruction**: the 1774-1912 segment is Officer &amp; Williamson's editorial splice of multiple historical series (Warren-Pearson wholesale price index reweighted to consumer proxy, etc.). The 1913+ segment is direct BLS CPI-U. We do not re-do the editorial splice — we use MeasuringWorth's published series as Shaikh did.</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr"/>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2. **License**: MeasuringWorth's permitted-academic-use license requires citing Officer &amp; Williamson and prohibits commercial redistribution. The post-1913 BLS CPI-U (FRED `CPIAUCNS`) is the open-license fallback for the modern segment; MeasuringWorth's pre-1913 segment is what makes the long-run series unique.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>## 8. Cross-references</t>
+          <t>3. **No proxy substitution**: Both subseries are CPI on the same base. The extension is the same BLS CPI-U that MeasuringWorth uses as its post-1913 backbone.</t>
         </is>
       </c>
     </row>
@@ -9676,38 +9676,38 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>- **CD legacy ID**: `S076` (same concept)</t>
+          <t>## 8. Cross-references</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>- **CD2 legacy ID**: `S076` (same concept; CD2 validation values 1774=7.82, 1899=8.04, 1949=23.85, 1999=166.60)</t>
-        </is>
-      </c>
+      <c r="A72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>- **Predecessor artifact**: `SalvagedInputs/extension_benchmarks/CD2_v1.3/Series/S076*.xlsx` (if present)</t>
+          <t>- **Predecessor-build ID**: `S076` (same concept)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>- **Book reference**: Shaikh (2016), Ch. 15, p. 696, Figure 15.1; Appendix 15.1 p. 895</t>
+          <t>- **Predecessor-build ID (second build)**: `S076` (same concept; second-build validation values 1774=7.82, 1899=8.04, 1949=23.85, 1999=166.60)</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr"/>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>- **Predecessor artifact**: `SalvagedInputs/extension_benchmarks/CD2_v1.3/Series/S076*.xlsx` (if present)</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>## 9. Validation expectation</t>
+          <t>- **Book reference**: Shaikh (2016), Ch. 15, p. 696, Figure 15.1; Appendix 15.1 p. 895</t>
         </is>
       </c>
     </row>
@@ -9717,96 +9717,96 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>- **Tolerance**: +/- 1.0% per year on the overlap range 1774-2011.</t>
+          <t>## 9. Validation expectation</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>- **Expected MAE** vs `Appendix15_MeasuringWorthCPI.xlsx` column `U.S. Consumer Price Index`: ~0 (we read the same column).</t>
-        </is>
-      </c>
+      <c r="A79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>- **CD2 informational comparison**: provided for the four spot-check years above.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="4">
+          <t>- **Tolerance**: +/- 1.0% per year on the overlap range 1774-2011.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>- **Expected mean absolute error (MAE)** vs `Appendix15_MeasuringWorthCPI.xlsx` column `U.S. Consumer Price Index`: ~0 (we read the same column).</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>- **Comparison with the predecessor build**: provided for the four spot-check years above.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4">
         <f>== EPR: S1501_EPR.md ===</f>
         <v/>
       </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t># S1501 — Extension Provenance Record</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>**Series**: S1501 — U.S. Consumer Price Index, 1774-2025</t>
+          <t># S1501 — Extension Provenance Record</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>**Phase**: 6 (Extension)</t>
-        </is>
-      </c>
+      <c r="A87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>**Construction classification**: `direct`</t>
+          <t>**Series**: S1501 — U.S. Consumer Price Index, 1774-2025</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>**Extension method**: overlap-anchor splice from FRED `CPIAUCNS` (BLS CPI-U), which is the same post-1913 backbone that MeasuringWorth's USCPI uses, on the same 1982-84 = 100 base</t>
+          <t>**Pipeline stage**: Extension</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>**Authored**: 2026-05-18</t>
+          <t>**Construction classification**: `direct`</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>**Author**: opus-subagent-fanout-ch15</t>
+          <t>**Extension method**: overlap-anchor splice from FRED `CPIAUCNS` (BLS CPI-U), which is the same post-1913 backbone that MeasuringWorth's USCPI uses, on the same 1982-84 = 100 base</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>**Related**: `S1501_DPR.md`, `Technical/research/S1501_research.json`, `Technical/SUBSOURCE_METADATA.json`</t>
+          <t>**Authored**: 2026-05-18</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr"/>
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>**Author**: RSCD replication pipeline (automated)</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>**Related**: `S1501_DPR.md`, `Technical/research/S1501_research.json`, `Technical/SUBSOURCE_METADATA.json`</t>
         </is>
       </c>
     </row>
@@ -9816,7 +9816,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>## 1. Why this series is extendable</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -9826,7 +9826,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>S1501 is a `time_series` series (per registry `content_type`). Both segments — MeasuringWorth USCPI (1774-2011) and BLS CPI-U (1913-present) — are continuously published. The post-1913 portion of MeasuringWorth IS BLS CPI-U, so the extension is a direct continuation of the same time series Shaikh used.</t>
+          <t>## 1. Why this series is extendable</t>
         </is>
       </c>
     </row>
@@ -9836,7 +9836,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>## 2. Construction classification</t>
+          <t>S1501 is a `time_series` series (per registry `content_type`). Both segments — MeasuringWorth USCPI (1774-2011) and BLS CPI-U (1913-present) — are continuously published. The post-1913 portion of MeasuringWorth IS BLS CPI-U, so the extension is a direct continuation of the same time series Shaikh used.</t>
         </is>
       </c>
     </row>
@@ -9846,7 +9846,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>S1501 is `direct`, not `formula`. The lazy-splice prohibition (Anu rule) is satisfied because we are appending the same observed BLS CPI-U index, not a growth rate computed on a derivative quantity.</t>
+          <t>## 2. Construction classification</t>
         </is>
       </c>
     </row>
@@ -9856,7 +9856,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>## 3. Method</t>
+          <t>S1501 is `direct`, not `formula`. This project's lazy-splice prohibition is satisfied because we are appending the same observed BLS CPI-U index, not a growth rate computed on a derivative quantity.</t>
         </is>
       </c>
     </row>
@@ -9866,124 +9866,124 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>```</t>
+          <t>## 3. Method</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>INPUTS</t>
-        </is>
-      </c>
+      <c r="A107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">  S1501_book      = MeasuringWorth USCPI 1774-2011, base 1982-84 = 100</t>
+          <t>```</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FRED_CPIAUCNS   = BLS CPI-U All Urban Consumers (NSA), annual avg, base 1982-84 = 100</t>
+          <t>INPUTS</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr"/>
+      <c r="A110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  S1501_book      = MeasuringWorth USCPI 1774-2011, base 1982-84 = 100</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>OVERLAP CHECK</t>
+          <t xml:space="preserve">  FRED_CPIAUCNS   = BLS CPI-U All Urban Consumers (NSA), annual avg, base 1982-84 = 100</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  overlap_year = 2011</t>
-        </is>
-      </c>
+      <c r="A112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Assert: S1501_book[2011] and FRED_CPIAUCNS[2011] both non-NaN</t>
+          <t>OVERLAP CHECK</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Walk back through 2010, 2009, ... 2005 if needed.</t>
+          <t xml:space="preserve">  overlap_year = 2011</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr"/>
+      <c r="A115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Assert: S1501_book[2011] and FRED_CPIAUCNS[2011] both non-NaN</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>REINDEX</t>
+          <t xml:space="preserve">  Walk back through 2010, 2009, ... 2005 if needed.</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  scale_factor = S1501_book[overlap_year] / FRED_CPIAUCNS[overlap_year]</t>
-        </is>
-      </c>
+      <c r="A117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">  S1501-B[year] = FRED_CPIAUCNS[year] * scale_factor   for year in [2012, 2025]</t>
+          <t>REINDEX</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr"/>
+      <c r="A119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  scale_factor = S1501_book[overlap_year] / FRED_CPIAUCNS[overlap_year]</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>SPLICE</t>
+          <t xml:space="preserve">  S1501-B[year] = FRED_CPIAUCNS[year] * scale_factor   for year in [2012, 2025]</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  S1501_extended[year] = S1501_book[year]    for year in [1774, 2011]</t>
-        </is>
-      </c>
+      <c r="A121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">  S1501_extended[year] = S1501-B[year]       for year in [2012, 2025]</t>
+          <t>SPLICE</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>```</t>
+          <t xml:space="preserve">  S1501_extended[year] = S1501_book[year]    for year in [1774, 2011]</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr"/>
+      <c r="A124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  S1501_extended[year] = S1501-B[year]       for year in [2012, 2025]</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Because both series are on the same 1982-84 base, `scale_factor` is expected to be ~1.000 (to within rounding); the explicit overlap-anchor calculation is retained for robustness against any future BLS rebase or revision.</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -9993,7 +9993,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>## 4. Worked example</t>
+          <t>Because both series are on the same 1982-84 base, `scale_factor` is expected to be ~1.000 (to within rounding); the explicit overlap-anchor calculation is retained for robustness against any future BLS rebase or revision.</t>
         </is>
       </c>
     </row>
@@ -10003,7 +10003,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>If `FRED_CPIAUCNS[2011] = 224.939` and `S1501_book[2011] = 224.94`, then `scale_factor = 224.94 / 224.939 = 1.000004`. Negligible adjustment.</t>
+          <t>## 4. Worked example</t>
         </is>
       </c>
     </row>
@@ -10013,7 +10013,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>## 5. Proxies</t>
+          <t>If `FRED_CPIAUCNS[2011] = 224.939` and `S1501_book[2011] = 224.94`, then `scale_factor = 224.94 / 224.939 = 1.000004`. Negligible adjustment.</t>
         </is>
       </c>
     </row>
@@ -10023,7 +10023,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>**None.** FRED `CPIAUCNS` is BLS CPI-U All Urban Consumers (NSA), the same series MeasuringWorth uses for its post-1913 segment. No concept substitution.</t>
+          <t>## 5. Proxies</t>
         </is>
       </c>
     </row>
@@ -10033,7 +10033,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>## 6. Synthetic data</t>
+          <t>**None.** FRED `CPIAUCNS` is BLS CPI-U All Urban Consumers (NSA), the same series MeasuringWorth uses for its post-1913 segment. No concept substitution.</t>
         </is>
       </c>
     </row>
@@ -10043,7 +10043,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>**None permitted.** NaNs propagate.</t>
+          <t>## 6. Synthetic data</t>
         </is>
       </c>
     </row>
@@ -10053,7 +10053,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>## 7. Failure modes &amp; graceful degradation</t>
+          <t>**None permitted.** NaNs propagate.</t>
         </is>
       </c>
     </row>
@@ -10063,45 +10063,45 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>| Failure | Detection | Action |</t>
+          <t>## 7. Failure modes &amp; graceful degradation</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>|---|---|---|</t>
-        </is>
-      </c>
+      <c r="A142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>| `FRED_API_KEY` not set | `S00_config` flags | Loader returns `{status: degraded, fred_status: missing_key}`; processor publishes 1774-2011 only; registry stamped `extension_status: api_key_missing` |</t>
+          <t>| Failure | Detection | Action |</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>| FRED API non-200 | `S00_apis.fred_observations()` raises | Retries 3x then degrades |</t>
+          <t>|---|---|---|</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>| FRED returns NaN at 2011 | Processor walks back through 2010, 2009, ... 2005 | If all NaN, FAIL hard |</t>
+          <t>| `FRED_API_KEY` not set | `S00_config` flags | Loader returns `{status: degraded, fred_status: missing_key}`; processor publishes 1774-2011 only; registry stamped `extension_status: api_key_missing` |</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr"/>
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>| FRED API non-200 | `S00_apis.fred_observations()` raises | Retries 3x then degrades |</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>## 8. CD2 divergence pre-disclosure</t>
+          <t>| FRED returns NaN at 2011 | Processor walks back through 2010, 2009, ... 2005 | If all NaN, FAIL hard |</t>
         </is>
       </c>
     </row>
@@ -10111,7 +10111,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>CD2's S076 used MeasuringWorth as well; level values should match exactly at the four spot-check years (1774, 1899, 1949, 1999). The validator reports this informationally.</t>
+          <t>## 8. Divergence from the predecessor build</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>The predecessor build's S076 used MeasuringWorth as well; level values should match exactly at the four spot-check years (1774, 1899, 1949, 1999). The validator reports this informationally.</t>
         </is>
       </c>
     </row>
@@ -10435,7 +10445,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-05-18T22:14:07.840935+00:00</t>
+          <t>2026-07-02T11:32:45.307079+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S1501_extenbook.xlsx
+++ b/extenbooks/S1501_extenbook.xlsx
@@ -9322,7 +9322,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: book_period_validated</t>
+          <t>**Status**: validated_book_and_extension</t>
         </is>
       </c>
     </row>
@@ -10445,7 +10445,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-02T11:32:45.307079+00:00</t>
+          <t>2026-07-11T03:44:23.252542+00:00</t>
         </is>
       </c>
     </row>
@@ -10460,11 +10460,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10487,6 +10487,150 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>MEASURINGWORTH_USCPI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>validated_book_and_extension</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Faithful direct replication of book figure 15.1 (consumer price level, US, 1774-2011), MeasuringWorth USCPI primary segment extended to 2025 via FRED CPIAUCNS. Contiguous annual index, units clean (index 1982-84=100), reference values verified. KB title/figure/quotes confirmed verbatim.", "date": "2026-06-11"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1501_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1501_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>time_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>index_1982_84=100</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
